--- a/eval_output/組二組_紀佩欣_評分表.xlsx
+++ b/eval_output/組二組_紀佩欣_評分表.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,11 +158,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -612,7 +619,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:M6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -708,15 +715,25 @@
           <t>0~30</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
     </row>
     <row r="9" ht="41" customHeight="1">
       <c r="A9" s="8" t="n"/>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>你對於受評者在日常表現上或各種會議中，對於受評者工作的『正確率』，達成百分比</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>10分100%
 9分  90%
@@ -730,7 +747,16 @@
 1分  10%</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
     </row>
     <row r="10" ht="77" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -738,19 +764,29 @@
           <t>工作表現40%</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
     </row>
     <row r="11" ht="77" customHeight="1">
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>你對於受評者在日常表現上或各種會議中，對於受評者工作的『完成度』，達成百分比</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>10分100%
 9分  90%
@@ -764,22 +800,41 @@
 1分  10%</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
     </row>
     <row r="12" ht="38.5" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
     </row>
     <row r="13" ht="38.5" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>受評者的工作品質</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>✓工作品質穩定準確無誤且高度可靠，能自我修正改善 (17-20)
 ✓工作品質持續保持高水準且幾乎無需他人協助或修正 (13-16)
@@ -789,22 +844,41 @@
 ✓工作品質極差，無法達到基本要求，缺乏改善能力與責任感 (0-1)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
     </row>
     <row r="14" ht="30.5" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於17分，請說明原因：___________________________</t>
         </is>
       </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
     </row>
     <row r="15" ht="30.5" customHeight="1">
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>【現場】「只限評分現場人員專用」</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">✓積極配合排班與加班，並能準時高品質完成工作 (10)
 ✓配合加班完成工作，偶有延遲但能解釋清楚且態度積極(8-9)
@@ -815,23 +889,42 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>*低於等於3分或高於等於8分，請說明原因：___________________________</t>
         </is>
       </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
     </row>
     <row r="17" ht="56.5" customHeight="1">
       <c r="A17" s="8" t="n"/>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>你對於受評者在日常任務完成表現</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>✓主動完成分內工作並協助同仁完成共同任務 (10)
 ✓始終保持高度積極性，主動尋找改進方法 (9)
@@ -842,27 +935,46 @@
 ✓缺乏熱情，無責任感，需不斷督促 (0)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>工作態度30%</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>*低於等於1分或高於等於9分，請說明原因：___________________</t>
         </is>
       </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
     </row>
     <row r="19" ht="45.5" customHeight="1">
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>是否願意和受評者一起工作?</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>✓我很願意跟受評者一起工作(8-10)
 ✓我還算願意跟受評者一起工作(5-7)
@@ -870,24 +982,79 @@
 ✓我不願意跟受評者一起工作(0-1)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>*低於等於1分或高於等於9分，請說明原因：__________________</t>
         </is>
       </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
     </row>
     <row r="21" ht="50.5" customHeight="1">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="21">
         <f>SUM(D8:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>SUM(E8:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>SUM(F8:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>SUM(G8:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="21">
+        <f>SUM(H8:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="21">
+        <f>SUM(I8:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="21">
+        <f>SUM(J8:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="21">
+        <f>SUM(K8:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="21">
+        <f>SUM(L8:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="21">
+        <f>SUM(M8:M20)</f>
         <v/>
       </c>
     </row>
@@ -902,8 +1069,99 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E22" s="6">
+        <f>IF(OR(
+  AND(E21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(E21&gt;=80,E21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(E21&gt;=70,E21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(E21&gt;=60,E21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(E21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F22" s="6">
+        <f>IF(OR(
+  AND(F21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(F21&gt;=80,F21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(F21&gt;=70,F21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(F21&gt;=60,F21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(F21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="G22" s="6">
+        <f>IF(OR(
+  AND(G21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(G21&gt;=80,G21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(G21&gt;=70,G21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(G21&gt;=60,G21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(G21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="H22" s="6">
+        <f>IF(OR(
+  AND(H21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(H21&gt;=80,H21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(H21&gt;=70,H21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(H21&gt;=60,H21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(H21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="I22" s="6">
+        <f>IF(OR(
+  AND(I21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(I21&gt;=80,I21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(I21&gt;=70,I21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(I21&gt;=60,I21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(I21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="J22" s="6">
+        <f>IF(OR(
+  AND(J21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(J21&gt;=80,J21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(J21&gt;=70,J21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(J21&gt;=60,J21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(J21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="K22" s="6">
+        <f>IF(OR(
+  AND(K21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(K21&gt;=80,K21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(K21&gt;=70,K21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(K21&gt;=60,K21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(K21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="L22" s="6">
+        <f>IF(OR(
+  AND(L21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(L21&gt;=80,L21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(L21&gt;=70,L21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(L21&gt;=60,L21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(L21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF(OR(
+  AND(M21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(M21&gt;=80,M21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(M21&gt;=70,M21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(M21&gt;=60,M21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(M21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="17">
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="D19:D20"/>
@@ -987,7 +1245,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:H6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1063,14 +1321,19 @@
 ✓不熟悉製程；錯誤率高；無法獨立作業或教導他人。(0-2) </t>
         </is>
       </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9" ht="84" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>產品知識與設備保養管理（10 分）</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">✓熟知產品規格、品質要求、主要不良模式；保養確實、設備狀況佳。 (9-10) 
 ✓了解基本產品要求；保養紀錄完整；偶需提醒。 (7-8) 
@@ -1079,6 +1342,11 @@
 ✓不不懂產品、不做保養；設備狀況差，影響產線運作。(0-2) </t>
         </is>
       </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10" ht="53" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1086,12 +1354,12 @@
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -1100,15 +1368,20 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11" ht="53" customHeight="1">
       <c r="A11" s="8" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>對於主管交辦的任務</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>✓對於主管交辦的任務均能完成 (15)
 ✓對於主管交辦的任務均能完成90%以上 (13-14)
@@ -1119,28 +1392,37 @@
 ✓對於主管交辦的任務常說”我不會、我不要、不是我”(0~1)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12" ht="57.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>工作態度
 30%</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>*低於等於3分或高於等於13分，請說明原因： __________________________</t>
         </is>
       </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>對於工作任務完成度</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>✓準時上下班工作均能完成 (14-15)
 ✓偶爾加班也能完成工作 (11-13)
@@ -1150,23 +1432,32 @@
 ✓雖經常加班但工作還是延遲完成 (0-1)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>*低於等於1或高於等於14分，請說明原因：___________________________</t>
         </is>
       </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n"/>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>※印象中你對受評者在指導與覆核部屬方面，願意給幾分</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">✓經常主動指導(領導)部屬 (16-20)
 ✓需經部屬提出並樂意指導(領導) (11-15)
@@ -1175,28 +1466,37 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>領導統御
 30%</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>*低於等於6分或高於等於16分，請說明原因：________________</t>
         </is>
       </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17" ht="50" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>是否願意和受評者一起工作?</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>✓我很願意跟受評者一起工作(8~10)
 ✓我還算願意跟受評者一起工作(5~7)
@@ -1204,24 +1504,49 @@
 ✓我不願意跟受評者一起工作(0-1)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>*低於等於3分或最高分，請敘述狀況：_________________________</t>
         </is>
       </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19" ht="50.5" customHeight="1">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="21">
         <f>SUM(D8:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>SUM(E8:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>SUM(F8:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>SUM(G8:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>SUM(H8:H18)</f>
         <v/>
       </c>
     </row>
@@ -1236,8 +1561,49 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E20" s="6">
+        <f>IF(OR(
+  AND(E19&gt;=90, COUNTIF($D$19:$Z$19, "&gt;=90")/COUNTA($D$19:$Z$19)&gt;0.05),
+  AND(E19&gt;=80,E19&lt;=89, (COUNTIF($D$19:$Z$19, "&gt;=80")-COUNTIF($D$19:$Z$19, "&gt;=90"))/COUNTA($D$19:$Z$19)&gt;0.2),
+  AND(E19&gt;=70,E19&lt;=79, (COUNTIF($D$19:$Z$19, "&gt;=70")-COUNTIF($D$19:$Z$19, "&gt;=80"))/COUNTA($D$19:$Z$19)&gt;0.4),
+  AND(E19&gt;=60,E19&lt;=69, (COUNTIF($D$19:$Z$19, "&gt;=60")-COUNTIF($D$19:$Z$19, "&gt;=70"))/COUNTA($D$19:$Z$19)&gt;0.3),
+  AND(E19&lt;=59, COUNTIF($D$19:$Z$19, "&lt;=59")/COUNTA($D$19:$Z$19)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F20" s="6">
+        <f>IF(OR(
+  AND(F19&gt;=90, COUNTIF($D$19:$Z$19, "&gt;=90")/COUNTA($D$19:$Z$19)&gt;0.05),
+  AND(F19&gt;=80,F19&lt;=89, (COUNTIF($D$19:$Z$19, "&gt;=80")-COUNTIF($D$19:$Z$19, "&gt;=90"))/COUNTA($D$19:$Z$19)&gt;0.2),
+  AND(F19&gt;=70,F19&lt;=79, (COUNTIF($D$19:$Z$19, "&gt;=70")-COUNTIF($D$19:$Z$19, "&gt;=80"))/COUNTA($D$19:$Z$19)&gt;0.4),
+  AND(F19&gt;=60,F19&lt;=69, (COUNTIF($D$19:$Z$19, "&gt;=60")-COUNTIF($D$19:$Z$19, "&gt;=70"))/COUNTA($D$19:$Z$19)&gt;0.3),
+  AND(F19&lt;=59, COUNTIF($D$19:$Z$19, "&lt;=59")/COUNTA($D$19:$Z$19)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="G20" s="6">
+        <f>IF(OR(
+  AND(G19&gt;=90, COUNTIF($D$19:$Z$19, "&gt;=90")/COUNTA($D$19:$Z$19)&gt;0.05),
+  AND(G19&gt;=80,G19&lt;=89, (COUNTIF($D$19:$Z$19, "&gt;=80")-COUNTIF($D$19:$Z$19, "&gt;=90"))/COUNTA($D$19:$Z$19)&gt;0.2),
+  AND(G19&gt;=70,G19&lt;=79, (COUNTIF($D$19:$Z$19, "&gt;=70")-COUNTIF($D$19:$Z$19, "&gt;=80"))/COUNTA($D$19:$Z$19)&gt;0.4),
+  AND(G19&gt;=60,G19&lt;=69, (COUNTIF($D$19:$Z$19, "&gt;=60")-COUNTIF($D$19:$Z$19, "&gt;=70"))/COUNTA($D$19:$Z$19)&gt;0.3),
+  AND(G19&lt;=59, COUNTIF($D$19:$Z$19, "&lt;=59")/COUNTA($D$19:$Z$19)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>IF(OR(
+  AND(H19&gt;=90, COUNTIF($D$19:$Z$19, "&gt;=90")/COUNTA($D$19:$Z$19)&gt;0.05),
+  AND(H19&gt;=80,H19&lt;=89, (COUNTIF($D$19:$Z$19, "&gt;=80")-COUNTIF($D$19:$Z$19, "&gt;=90"))/COUNTA($D$19:$Z$19)&gt;0.2),
+  AND(H19&gt;=70,H19&lt;=79, (COUNTIF($D$19:$Z$19, "&gt;=70")-COUNTIF($D$19:$Z$19, "&gt;=80"))/COUNTA($D$19:$Z$19)&gt;0.4),
+  AND(H19&gt;=60,H19&lt;=69, (COUNTIF($D$19:$Z$19, "&gt;=60")-COUNTIF($D$19:$Z$19, "&gt;=70"))/COUNTA($D$19:$Z$19)&gt;0.3),
+  AND(H19&lt;=59, COUNTIF($D$19:$Z$19, "&lt;=59")/COUNTA($D$19:$Z$19)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="14">
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="A12:A14"/>
